--- a/Resources/SleepyPsycastEffects.xlsx
+++ b/Resources/SleepyPsycastEffects.xlsx
@@ -771,11 +771,6 @@
 Incoming Damage Factor x110%
 Melee Dodge Chance -4 Levels</t>
     </r>
-  </si>
-  <si>
-    <t>Shooting Accuracy Pawn +3.0
-ShootingAccuracyFactor_Medium +0.5%
-ShootingAccuracyFactor_Long  +1% (Makes a much bigger difference then suggested)</t>
   </si>
   <si>
     <t>Hypothermia set to 50%</t>
@@ -918,6 +913,11 @@
   <si>
     <t xml:space="preserve">30.0 Days - Phoenix Syndrome
 RNG: 1.5 to 2.5 Days -Resurrection Sickness </t>
+  </si>
+  <si>
+    <t>Shooting Accuracy Pawn +3.0
+ShootingAccuracyFactor_Medium +25%
+ShootingAccuracyFactor_Long  +50%</t>
   </si>
 </sst>
 </file>
@@ -3264,7 +3264,7 @@
         <v>23</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F36" s="3">
         <v>5</v>
@@ -3341,7 +3341,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>107</v>
@@ -3438,7 +3438,7 @@
         <v>43</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="45">
@@ -3632,7 +3632,7 @@
         <v>34</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
@@ -3974,7 +3974,7 @@
         <v>180</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K51" s="16">
         <v>1.5</v>
@@ -4006,7 +4006,7 @@
         <v>18</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F52" s="6">
         <v>2</v>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:16" s="2" customFormat="1" ht="90">
+    <row r="53" spans="2:16" s="2" customFormat="1" ht="75">
       <c r="B53" s="43" t="s">
         <v>190</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="F53" s="6">
         <v>2</v>
@@ -4094,7 +4094,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6">
         <v>3</v>
@@ -4141,7 +4141,7 @@
         <v>18</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F55" s="6">
         <v>3</v>
@@ -4293,7 +4293,7 @@
         <v>336</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K58" s="16">
         <v>3</v>
@@ -4325,7 +4325,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59" s="6">
         <v>5</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K59" s="16">
         <v>0.1</v>
@@ -4715,7 +4715,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F4" s="6">
         <v>3</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F8" s="6">
         <v>6</v>
@@ -4930,7 +4930,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="10" spans="2:16" ht="45">
       <c r="B10" s="43" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>145</v>
@@ -4973,7 +4973,7 @@
         <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F10" s="3">
         <v>3</v>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="11" spans="2:16" ht="30">
       <c r="B11" s="43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>145</v>
@@ -5020,7 +5020,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F11" s="45">
         <v>6</v>
